--- a/worklog/v2.2.3/s10/pjm/v3/test/ods_progress_measure_v2.xlsx
+++ b/worklog/v2.2.3/s10/pjm/v3/test/ods_progress_measure_v2.xlsx
@@ -421,133 +421,133 @@
     <t>仿真结果满足设计要求</t>
   </si>
   <si>
+    <t>PJ-2025-004</t>
+  </si>
+  <si>
+    <t>PJ-2025-007</t>
+  </si>
+  <si>
+    <t>20250/04/25</t>
+  </si>
+  <si>
+    <t>待定</t>
+  </si>
+  <si>
+    <t>赵敏</t>
+  </si>
+  <si>
+    <t>PJ-2025-005</t>
+  </si>
+  <si>
+    <t>20250/04/12</t>
+  </si>
+  <si>
+    <t>黄磊</t>
+  </si>
+  <si>
+    <t>PJ-2025-006</t>
+  </si>
+  <si>
+    <t>2025年4月10日</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>PJ-2025-003</t>
+  </si>
+  <si>
+    <t>2025.3.15</t>
+  </si>
+  <si>
+    <t>秦川</t>
+  </si>
+  <si>
+    <t>2025/4/10</t>
+  </si>
+  <si>
+    <t>2025-13-22</t>
+  </si>
+  <si>
+    <t>2025.4.20</t>
+  </si>
+  <si>
+    <t>PJ-2025-008</t>
+  </si>
+  <si>
+    <t>未知</t>
+  </si>
+  <si>
+    <t>林小明</t>
+  </si>
+  <si>
+    <t>2025/04/12</t>
+  </si>
+  <si>
+    <t>2025/04/18</t>
+  </si>
+  <si>
+    <t>2025/03/01</t>
+  </si>
+  <si>
+    <t>郭伟</t>
+  </si>
+  <si>
+    <t>李雪</t>
+  </si>
+  <si>
+    <t>2025-02-30</t>
+  </si>
+  <si>
+    <t>2025-4-10</t>
+  </si>
+  <si>
+    <t>2025/3/15</t>
+  </si>
+  <si>
+    <t>20205/05/15</t>
+  </si>
+  <si>
     <t>王鹏</t>
   </si>
   <si>
-    <t>待定</t>
-  </si>
-  <si>
-    <t>PJ-2025-006</t>
-  </si>
-  <si>
-    <t>2025-03</t>
-  </si>
-  <si>
-    <t>20250/04/09</t>
-  </si>
-  <si>
-    <t>PJ-2025-007</t>
-  </si>
-  <si>
-    <t>未知</t>
-  </si>
-  <si>
-    <t>郭伟</t>
-  </si>
-  <si>
-    <t>秦川</t>
-  </si>
-  <si>
-    <t>PJ-2025-003</t>
-  </si>
-  <si>
-    <t>2025-04-32</t>
-  </si>
-  <si>
-    <t>PJ-2025-005</t>
-  </si>
-  <si>
-    <t>PJ-2025-004</t>
+    <t>20205/04/25</t>
   </si>
   <si>
     <t>2025-04</t>
   </si>
   <si>
-    <t>李雪</t>
-  </si>
-  <si>
-    <t>2025/4/18</t>
-  </si>
-  <si>
     <t>钱海</t>
   </si>
   <si>
-    <t>2025-3-15</t>
-  </si>
-  <si>
-    <t>黄磊</t>
-  </si>
-  <si>
-    <t>赵敏</t>
-  </si>
-  <si>
-    <t>2025年4月9日</t>
+    <t>20205/04/09</t>
+  </si>
+  <si>
+    <t>2025-13-15</t>
+  </si>
+  <si>
+    <t>20205/05/20</t>
+  </si>
+  <si>
+    <t>2025年9月15日</t>
+  </si>
+  <si>
+    <t>20250/04/20</t>
+  </si>
+  <si>
+    <t>2025-4-5</t>
+  </si>
+  <si>
+    <t>20205/03/31</t>
+  </si>
+  <si>
+    <t>2025-13-09</t>
   </si>
   <si>
     <t>2025/06/05</t>
   </si>
   <si>
-    <t>2025-02-30</t>
-  </si>
-  <si>
-    <t>2025年04月20日</t>
-  </si>
-  <si>
-    <t>2025/04/25</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>PJ-2025-008</t>
-  </si>
-  <si>
-    <t>2025年4月8日</t>
-  </si>
-  <si>
-    <t>林小明</t>
-  </si>
-  <si>
-    <t>2025年6月5日</t>
-  </si>
-  <si>
-    <t>2025-13-31</t>
-  </si>
-  <si>
-    <t>2025-4-10</t>
-  </si>
-  <si>
-    <t>2025-4-12</t>
-  </si>
-  <si>
-    <t>2025/4/25</t>
-  </si>
-  <si>
-    <t>2025年3月1日</t>
-  </si>
-  <si>
-    <t>2025-3-5</t>
-  </si>
-  <si>
-    <t>2025/03/15</t>
-  </si>
-  <si>
-    <t>2025-13-05</t>
-  </si>
-  <si>
-    <t>20205/03/31</t>
-  </si>
-  <si>
-    <t>2025/4/8</t>
-  </si>
-  <si>
-    <t>2025-13-10</t>
-  </si>
-  <si>
-    <t>2025-6-5</t>
-  </si>
-  <si>
-    <t>20250/04/10</t>
+    <t>20205/04/20</t>
   </si>
 </sst>
 </file>
@@ -1338,7 +1338,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
@@ -1404,12 +1404,12 @@
         <v>38</v>
       </c>
       <c r="W12" t="s">
-        <v>137</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -1442,7 +1442,7 @@
         <v>41</v>
       </c>
       <c r="L13" t="s">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="M13" t="s">
         <v>35</v>
@@ -1466,7 +1466,7 @@
         <v>36</v>
       </c>
       <c r="T13" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="U13" t="s">
         <v>45</v>
@@ -1475,12 +1475,12 @@
         <v>48</v>
       </c>
       <c r="W13" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>139</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
         <v>49</v>
@@ -1489,7 +1489,7 @@
         <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>140</v>
       </c>
       <c r="E14" t="s">
         <v>52</v>
@@ -1537,7 +1537,7 @@
         <v>63</v>
       </c>
       <c r="T14" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="U14" t="s">
         <v>61</v>
@@ -1546,12 +1546,12 @@
         <v>36</v>
       </c>
       <c r="W14" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B15" t="s">
         <v>49</v>
@@ -1560,7 +1560,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>51</v>
       </c>
       <c r="E15" t="s">
         <v>52</v>
@@ -1593,7 +1593,7 @@
         <v>43</v>
       </c>
       <c r="O15" t="s">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="P15" t="s">
         <v>61</v>
@@ -1617,7 +1617,7 @@
         <v>71</v>
       </c>
       <c r="W15" t="s">
-        <v>31</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16">
@@ -1679,7 +1679,7 @@
         <v>36</v>
       </c>
       <c r="T16" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="U16" t="s">
         <v>61</v>
@@ -1688,12 +1688,12 @@
         <v>86</v>
       </c>
       <c r="W16" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B17" t="s">
         <v>72</v>
@@ -1702,7 +1702,7 @@
         <v>87</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>146</v>
       </c>
       <c r="E17" t="s">
         <v>61</v>
@@ -1726,7 +1726,7 @@
         <v>57</v>
       </c>
       <c r="L17" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="M17" t="s">
         <v>27</v>
@@ -1764,7 +1764,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B18" t="s">
         <v>49</v>
@@ -1821,7 +1821,7 @@
         <v>103</v>
       </c>
       <c r="T18" t="s">
-        <v>100</v>
+        <v>149</v>
       </c>
       <c r="U18" t="s">
         <v>101</v>
@@ -1830,12 +1830,12 @@
         <v>36</v>
       </c>
       <c r="W18" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="B19" t="s">
         <v>104</v>
@@ -1901,12 +1901,12 @@
         <v>115</v>
       </c>
       <c r="W19" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
@@ -1972,12 +1972,12 @@
         <v>126</v>
       </c>
       <c r="W20" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="B21" t="s">
         <v>127</v>
@@ -2010,7 +2010,7 @@
         <v>98</v>
       </c>
       <c r="L21" t="s">
-        <v>60</v>
+        <v>151</v>
       </c>
       <c r="M21" t="s">
         <v>61</v>
@@ -2043,12 +2043,12 @@
         <v>136</v>
       </c>
       <c r="W21" t="s">
-        <v>79</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="B22" t="s">
         <v>24</v>
@@ -2057,7 +2057,7 @@
         <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>147</v>
+        <v>26</v>
       </c>
       <c r="E22" t="s">
         <v>27</v>
@@ -2081,7 +2081,7 @@
         <v>33</v>
       </c>
       <c r="L22" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M22" t="s">
         <v>35</v>
@@ -2105,7 +2105,7 @@
         <v>37</v>
       </c>
       <c r="T22" t="s">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="U22" t="s">
         <v>35</v>
@@ -2114,7 +2114,7 @@
         <v>38</v>
       </c>
       <c r="W22" t="s">
-        <v>79</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23">
@@ -2128,7 +2128,7 @@
         <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>153</v>
       </c>
       <c r="E23" t="s">
         <v>27</v>
@@ -2190,7 +2190,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B24" t="s">
         <v>49</v>
@@ -2256,7 +2256,7 @@
         <v>36</v>
       </c>
       <c r="W24" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25">
@@ -2294,7 +2294,7 @@
         <v>66</v>
       </c>
       <c r="L25" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M25" t="s">
         <v>61</v>
@@ -2318,7 +2318,7 @@
         <v>36</v>
       </c>
       <c r="T25" t="s">
-        <v>143</v>
+        <v>68</v>
       </c>
       <c r="U25" t="s">
         <v>61</v>
@@ -2327,12 +2327,12 @@
         <v>71</v>
       </c>
       <c r="W25" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B26" t="s">
         <v>72</v>
@@ -2374,7 +2374,7 @@
         <v>43</v>
       </c>
       <c r="O26" t="s">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="P26" t="s">
         <v>61</v>
@@ -2398,7 +2398,7 @@
         <v>86</v>
       </c>
       <c r="W26" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27">
@@ -2460,7 +2460,7 @@
         <v>91</v>
       </c>
       <c r="T27" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="U27" t="s">
         <v>27</v>
@@ -2469,12 +2469,12 @@
         <v>92</v>
       </c>
       <c r="W27" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B28" t="s">
         <v>49</v>
@@ -2483,7 +2483,7 @@
         <v>94</v>
       </c>
       <c r="D28" t="s">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="E28" t="s">
         <v>96</v>
@@ -2531,7 +2531,7 @@
         <v>103</v>
       </c>
       <c r="T28" t="s">
-        <v>154</v>
+        <v>100</v>
       </c>
       <c r="U28" t="s">
         <v>101</v>
@@ -2540,7 +2540,7 @@
         <v>36</v>
       </c>
       <c r="W28" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29">
@@ -2611,12 +2611,12 @@
         <v>115</v>
       </c>
       <c r="W29" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B30" t="s">
         <v>24</v>
@@ -2682,12 +2682,12 @@
         <v>126</v>
       </c>
       <c r="W30" t="s">
-        <v>31</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B31" t="s">
         <v>127</v>
@@ -2729,7 +2729,7 @@
         <v>43</v>
       </c>
       <c r="O31" t="s">
-        <v>26</v>
+        <v>140</v>
       </c>
       <c r="P31" t="s">
         <v>27</v>
@@ -2753,12 +2753,12 @@
         <v>136</v>
       </c>
       <c r="W31" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>139</v>
+        <v>23</v>
       </c>
       <c r="B32" t="s">
         <v>24</v>
@@ -2815,7 +2815,7 @@
         <v>37</v>
       </c>
       <c r="T32" t="s">
-        <v>150</v>
+        <v>34</v>
       </c>
       <c r="U32" t="s">
         <v>35</v>
@@ -2824,12 +2824,12 @@
         <v>38</v>
       </c>
       <c r="W32" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B33" t="s">
         <v>24</v>
@@ -2895,12 +2895,12 @@
         <v>48</v>
       </c>
       <c r="W33" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B34" t="s">
         <v>49</v>
@@ -2966,12 +2966,12 @@
         <v>36</v>
       </c>
       <c r="W34" t="s">
-        <v>156</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B35" t="s">
         <v>49</v>
@@ -3013,7 +3013,7 @@
         <v>43</v>
       </c>
       <c r="O35" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="P35" t="s">
         <v>61</v>
@@ -3037,12 +3037,12 @@
         <v>71</v>
       </c>
       <c r="W35" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>146</v>
+        <v>93</v>
       </c>
       <c r="B36" t="s">
         <v>72</v>
@@ -3084,7 +3084,7 @@
         <v>43</v>
       </c>
       <c r="O36" t="s">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="P36" t="s">
         <v>61</v>
@@ -3099,7 +3099,7 @@
         <v>36</v>
       </c>
       <c r="T36" t="s">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="U36" t="s">
         <v>61</v>
@@ -3108,12 +3108,12 @@
         <v>86</v>
       </c>
       <c r="W36" t="s">
-        <v>55</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B37" t="s">
         <v>72</v>
@@ -3122,7 +3122,7 @@
         <v>87</v>
       </c>
       <c r="D37" t="s">
-        <v>60</v>
+        <v>163</v>
       </c>
       <c r="E37" t="s">
         <v>61</v>
@@ -3179,12 +3179,12 @@
         <v>92</v>
       </c>
       <c r="W37" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="B38" t="s">
         <v>49</v>
@@ -3241,7 +3241,7 @@
         <v>103</v>
       </c>
       <c r="T38" t="s">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="U38" t="s">
         <v>101</v>
@@ -3250,12 +3250,12 @@
         <v>36</v>
       </c>
       <c r="W38" t="s">
-        <v>79</v>
+        <v>160</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="B39" t="s">
         <v>104</v>
@@ -3264,7 +3264,7 @@
         <v>105</v>
       </c>
       <c r="D39" t="s">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="E39" t="s">
         <v>107</v>
@@ -3321,12 +3321,12 @@
         <v>115</v>
       </c>
       <c r="W39" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B40" t="s">
         <v>24</v>
@@ -3383,7 +3383,7 @@
         <v>125</v>
       </c>
       <c r="T40" t="s">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="U40" t="s">
         <v>124</v>
@@ -3392,12 +3392,12 @@
         <v>126</v>
       </c>
       <c r="W40" t="s">
-        <v>144</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B41" t="s">
         <v>127</v>
@@ -3406,7 +3406,7 @@
         <v>128</v>
       </c>
       <c r="D41" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="E41" t="s">
         <v>130</v>
@@ -3454,7 +3454,7 @@
         <v>36</v>
       </c>
       <c r="T41" t="s">
-        <v>160</v>
+        <v>26</v>
       </c>
       <c r="U41" t="s">
         <v>27</v>
@@ -3463,12 +3463,12 @@
         <v>136</v>
       </c>
       <c r="W41" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B42" t="s">
         <v>24</v>
@@ -3534,12 +3534,12 @@
         <v>38</v>
       </c>
       <c r="W42" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="B43" t="s">
         <v>24</v>
@@ -3572,7 +3572,7 @@
         <v>41</v>
       </c>
       <c r="L43" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="M43" t="s">
         <v>35</v>
@@ -3596,7 +3596,7 @@
         <v>36</v>
       </c>
       <c r="T43" t="s">
-        <v>162</v>
+        <v>44</v>
       </c>
       <c r="U43" t="s">
         <v>45</v>
@@ -3605,12 +3605,12 @@
         <v>48</v>
       </c>
       <c r="W43" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="B44" t="s">
         <v>49</v>
@@ -3667,7 +3667,7 @@
         <v>63</v>
       </c>
       <c r="T44" t="s">
-        <v>60</v>
+        <v>168</v>
       </c>
       <c r="U44" t="s">
         <v>61</v>
@@ -3676,12 +3676,12 @@
         <v>36</v>
       </c>
       <c r="W44" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="B45" t="s">
         <v>49</v>
@@ -3714,7 +3714,7 @@
         <v>66</v>
       </c>
       <c r="L45" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="M45" t="s">
         <v>61</v>
@@ -3747,7 +3747,7 @@
         <v>71</v>
       </c>
       <c r="W45" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46">
@@ -3818,12 +3818,12 @@
         <v>86</v>
       </c>
       <c r="W46" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B47" t="s">
         <v>72</v>
@@ -3880,7 +3880,7 @@
         <v>91</v>
       </c>
       <c r="T47" t="s">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="U47" t="s">
         <v>27</v>
@@ -3889,12 +3889,12 @@
         <v>92</v>
       </c>
       <c r="W47" t="s">
-        <v>165</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="B48" t="s">
         <v>49</v>
@@ -3960,12 +3960,12 @@
         <v>36</v>
       </c>
       <c r="W48" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>163</v>
+        <v>93</v>
       </c>
       <c r="B49" t="s">
         <v>104</v>
@@ -4031,12 +4031,12 @@
         <v>115</v>
       </c>
       <c r="W49" t="s">
-        <v>133</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>23</v>
+        <v>148</v>
       </c>
       <c r="B50" t="s">
         <v>24</v>
@@ -4093,7 +4093,7 @@
         <v>125</v>
       </c>
       <c r="T50" t="s">
-        <v>166</v>
+        <v>123</v>
       </c>
       <c r="U50" t="s">
         <v>124</v>
@@ -4102,12 +4102,12 @@
         <v>126</v>
       </c>
       <c r="W50" t="s">
-        <v>31</v>
+        <v>150</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>149</v>
+        <v>93</v>
       </c>
       <c r="B51" t="s">
         <v>127</v>
@@ -4173,12 +4173,12 @@
         <v>136</v>
       </c>
       <c r="W51" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="B52" t="s">
         <v>24</v>
@@ -4187,7 +4187,7 @@
         <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>26</v>
+        <v>153</v>
       </c>
       <c r="E52" t="s">
         <v>27</v>
@@ -4235,7 +4235,7 @@
         <v>37</v>
       </c>
       <c r="T52" t="s">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c r="U52" t="s">
         <v>35</v>
@@ -4244,12 +4244,12 @@
         <v>38</v>
       </c>
       <c r="W52" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B53" t="s">
         <v>24</v>
@@ -4315,12 +4315,12 @@
         <v>48</v>
       </c>
       <c r="W53" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B54" t="s">
         <v>49</v>
@@ -4329,7 +4329,7 @@
         <v>50</v>
       </c>
       <c r="D54" t="s">
-        <v>167</v>
+        <v>51</v>
       </c>
       <c r="E54" t="s">
         <v>52</v>
@@ -4377,7 +4377,7 @@
         <v>63</v>
       </c>
       <c r="T54" t="s">
-        <v>168</v>
+        <v>60</v>
       </c>
       <c r="U54" t="s">
         <v>61</v>
@@ -4386,12 +4386,12 @@
         <v>36</v>
       </c>
       <c r="W54" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B55" t="s">
         <v>49</v>
@@ -4400,7 +4400,7 @@
         <v>50</v>
       </c>
       <c r="D55" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="E55" t="s">
         <v>52</v>
@@ -4448,7 +4448,7 @@
         <v>36</v>
       </c>
       <c r="T55" t="s">
-        <v>68</v>
+        <v>170</v>
       </c>
       <c r="U55" t="s">
         <v>61</v>
@@ -4457,12 +4457,12 @@
         <v>71</v>
       </c>
       <c r="W55" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="B56" t="s">
         <v>72</v>
@@ -4519,7 +4519,7 @@
         <v>36</v>
       </c>
       <c r="T56" t="s">
-        <v>169</v>
+        <v>83</v>
       </c>
       <c r="U56" t="s">
         <v>61</v>
@@ -4528,12 +4528,12 @@
         <v>86</v>
       </c>
       <c r="W56" t="s">
-        <v>151</v>
+        <v>109</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>148</v>
+        <v>23</v>
       </c>
       <c r="B57" t="s">
         <v>72</v>
@@ -4566,7 +4566,7 @@
         <v>57</v>
       </c>
       <c r="L57" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="M57" t="s">
         <v>27</v>
@@ -4599,7 +4599,7 @@
         <v>92</v>
       </c>
       <c r="W57" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
     </row>
     <row r="58">
@@ -4646,7 +4646,7 @@
         <v>43</v>
       </c>
       <c r="O58" t="s">
-        <v>100</v>
+        <v>171</v>
       </c>
       <c r="P58" t="s">
         <v>101</v>
@@ -4670,12 +4670,12 @@
         <v>36</v>
       </c>
       <c r="W58" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B59" t="s">
         <v>104</v>
@@ -4708,7 +4708,7 @@
         <v>111</v>
       </c>
       <c r="L59" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
       <c r="M59" t="s">
         <v>113</v>
@@ -4741,12 +4741,12 @@
         <v>115</v>
       </c>
       <c r="W59" t="s">
-        <v>31</v>
+        <v>169</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>163</v>
+        <v>23</v>
       </c>
       <c r="B60" t="s">
         <v>24</v>
@@ -4812,12 +4812,12 @@
         <v>126</v>
       </c>
       <c r="W60" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="B61" t="s">
         <v>127</v>
@@ -4826,7 +4826,7 @@
         <v>128</v>
       </c>
       <c r="D61" t="s">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="E61" t="s">
         <v>130</v>
@@ -4859,7 +4859,7 @@
         <v>43</v>
       </c>
       <c r="O61" t="s">
-        <v>26</v>
+        <v>174</v>
       </c>
       <c r="P61" t="s">
         <v>27</v>
@@ -4874,7 +4874,7 @@
         <v>36</v>
       </c>
       <c r="T61" t="s">
-        <v>26</v>
+        <v>155</v>
       </c>
       <c r="U61" t="s">
         <v>27</v>
@@ -4883,12 +4883,12 @@
         <v>136</v>
       </c>
       <c r="W61" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B62" t="s">
         <v>24</v>
@@ -4921,7 +4921,7 @@
         <v>33</v>
       </c>
       <c r="L62" t="s">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="M62" t="s">
         <v>35</v>
@@ -4954,12 +4954,12 @@
         <v>38</v>
       </c>
       <c r="W62" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="B63" t="s">
         <v>24</v>
@@ -4992,7 +4992,7 @@
         <v>41</v>
       </c>
       <c r="L63" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="M63" t="s">
         <v>35</v>
@@ -5025,12 +5025,12 @@
         <v>48</v>
       </c>
       <c r="W63" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="B64" t="s">
         <v>49</v>
@@ -5063,7 +5063,7 @@
         <v>57</v>
       </c>
       <c r="L64" t="s">
-        <v>58</v>
+        <v>175</v>
       </c>
       <c r="M64" t="s">
         <v>59</v>
@@ -5096,7 +5096,7 @@
         <v>36</v>
       </c>
       <c r="W64" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
     </row>
     <row r="65">
@@ -5110,7 +5110,7 @@
         <v>50</v>
       </c>
       <c r="D65" t="s">
-        <v>51</v>
+        <v>176</v>
       </c>
       <c r="E65" t="s">
         <v>52</v>
@@ -5143,7 +5143,7 @@
         <v>43</v>
       </c>
       <c r="O65" t="s">
-        <v>68</v>
+        <v>177</v>
       </c>
       <c r="P65" t="s">
         <v>61</v>
@@ -5167,12 +5167,12 @@
         <v>71</v>
       </c>
       <c r="W65" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="B66" t="s">
         <v>72</v>
@@ -5214,7 +5214,7 @@
         <v>43</v>
       </c>
       <c r="O66" t="s">
-        <v>169</v>
+        <v>83</v>
       </c>
       <c r="P66" t="s">
         <v>61</v>
@@ -5229,7 +5229,7 @@
         <v>36</v>
       </c>
       <c r="T66" t="s">
-        <v>83</v>
+        <v>168</v>
       </c>
       <c r="U66" t="s">
         <v>61</v>
@@ -5238,7 +5238,7 @@
         <v>86</v>
       </c>
       <c r="W66" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="67">
@@ -5309,12 +5309,12 @@
         <v>92</v>
       </c>
       <c r="W67" t="s">
-        <v>151</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B68" t="s">
         <v>49</v>
@@ -5323,7 +5323,7 @@
         <v>94</v>
       </c>
       <c r="D68" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
       <c r="E68" t="s">
         <v>96</v>
@@ -5347,7 +5347,7 @@
         <v>98</v>
       </c>
       <c r="L68" t="s">
-        <v>172</v>
+        <v>99</v>
       </c>
       <c r="M68" t="s">
         <v>75</v>
@@ -5356,7 +5356,7 @@
         <v>43</v>
       </c>
       <c r="O68" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="P68" t="s">
         <v>101</v>
@@ -5371,7 +5371,7 @@
         <v>103</v>
       </c>
       <c r="T68" t="s">
-        <v>100</v>
+        <v>149</v>
       </c>
       <c r="U68" t="s">
         <v>101</v>
@@ -5380,12 +5380,12 @@
         <v>36</v>
       </c>
       <c r="W68" t="s">
-        <v>109</v>
+        <v>156</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="B69" t="s">
         <v>104</v>
@@ -5394,7 +5394,7 @@
         <v>105</v>
       </c>
       <c r="D69" t="s">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="E69" t="s">
         <v>107</v>
@@ -5451,12 +5451,12 @@
         <v>115</v>
       </c>
       <c r="W69" t="s">
-        <v>144</v>
+        <v>79</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B70" t="s">
         <v>24</v>
@@ -5489,7 +5489,7 @@
         <v>122</v>
       </c>
       <c r="L70" t="s">
-        <v>138</v>
+        <v>178</v>
       </c>
       <c r="M70" t="s">
         <v>124</v>
@@ -5513,7 +5513,7 @@
         <v>125</v>
       </c>
       <c r="T70" t="s">
-        <v>174</v>
+        <v>123</v>
       </c>
       <c r="U70" t="s">
         <v>124</v>
@@ -5522,12 +5522,12 @@
         <v>126</v>
       </c>
       <c r="W70" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="B71" t="s">
         <v>127</v>
@@ -5593,7 +5593,7 @@
         <v>136</v>
       </c>
       <c r="W71" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
     </row>
     <row r="72">
@@ -5664,12 +5664,12 @@
         <v>38</v>
       </c>
       <c r="W72" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>148</v>
+        <v>93</v>
       </c>
       <c r="B73" t="s">
         <v>24</v>
@@ -5735,12 +5735,12 @@
         <v>48</v>
       </c>
       <c r="W73" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="B74" t="s">
         <v>49</v>
@@ -5811,7 +5811,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B75" t="s">
         <v>49</v>
@@ -5820,7 +5820,7 @@
         <v>50</v>
       </c>
       <c r="D75" t="s">
-        <v>175</v>
+        <v>51</v>
       </c>
       <c r="E75" t="s">
         <v>52</v>
@@ -5844,7 +5844,7 @@
         <v>66</v>
       </c>
       <c r="L75" t="s">
-        <v>176</v>
+        <v>67</v>
       </c>
       <c r="M75" t="s">
         <v>61</v>
@@ -5877,12 +5877,12 @@
         <v>71</v>
       </c>
       <c r="W75" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="B76" t="s">
         <v>72</v>
@@ -5891,7 +5891,7 @@
         <v>73</v>
       </c>
       <c r="D76" t="s">
-        <v>177</v>
+        <v>74</v>
       </c>
       <c r="E76" t="s">
         <v>75</v>
@@ -5948,12 +5948,12 @@
         <v>86</v>
       </c>
       <c r="W76" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="B77" t="s">
         <v>72</v>
@@ -6019,12 +6019,12 @@
         <v>92</v>
       </c>
       <c r="W77" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B78" t="s">
         <v>49</v>
@@ -6090,12 +6090,12 @@
         <v>36</v>
       </c>
       <c r="W78" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B79" t="s">
         <v>104</v>
@@ -6161,12 +6161,12 @@
         <v>115</v>
       </c>
       <c r="W79" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B80" t="s">
         <v>24</v>
@@ -6199,7 +6199,7 @@
         <v>122</v>
       </c>
       <c r="L80" t="s">
-        <v>178</v>
+        <v>123</v>
       </c>
       <c r="M80" t="s">
         <v>124</v>
@@ -6232,12 +6232,12 @@
         <v>126</v>
       </c>
       <c r="W80" t="s">
-        <v>31</v>
+        <v>141</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B81" t="s">
         <v>127</v>
@@ -6270,7 +6270,7 @@
         <v>98</v>
       </c>
       <c r="L81" t="s">
-        <v>179</v>
+        <v>60</v>
       </c>
       <c r="M81" t="s">
         <v>61</v>
@@ -6294,7 +6294,7 @@
         <v>36</v>
       </c>
       <c r="T81" t="s">
-        <v>26</v>
+        <v>179</v>
       </c>
       <c r="U81" t="s">
         <v>27</v>
@@ -6303,7 +6303,7 @@
         <v>136</v>
       </c>
       <c r="W81" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
